--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8387096774193549</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.704225352112676</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="D2">
-        <v>0.35</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="E2">
         <v>93</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
